--- a/data/trans_bre/P2A_fisi_R-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/P2A_fisi_R-Provincia-trans_bre.xlsx
@@ -602,7 +602,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Almeria</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -660,22 +660,22 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-7,65; 1,24</t>
+          <t>-7,46; 2,02</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-15,02; 1,68</t>
+          <t>-16,88; 0,6</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-10,25; 4,61</t>
+          <t>-9,06; 4,68</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-9,61; -0,18</t>
+          <t>-9,3; 0,08</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -690,7 +690,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 274,27</t>
+          <t>-100,0; 276,31</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -702,7 +702,7 @@
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>Cadiz</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -760,22 +760,22 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-6,69; 3,46</t>
+          <t>-6,66; 3,24</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-9,76; 0,2</t>
+          <t>-9,68; 0,2</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-2,26; 7,49</t>
+          <t>-1,84; 9,36</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-6,55; 5,99</t>
+          <t>-6,23; 6,0</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; —</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -795,14 +795,14 @@
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-67,76; 209,67</t>
+          <t>-71,88; 209,75</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Cordoba</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-4,95; 4,43</t>
+          <t>-6,02; 3,3</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -875,7 +875,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-13,15; 0,61</t>
+          <t>-13,4; 0,93</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -895,7 +895,7 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-90,91; 27,93</t>
+          <t>-91,98; 37,55</t>
         </is>
       </c>
     </row>
@@ -960,22 +960,22 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-3,28; 3,22</t>
+          <t>-3,25; 3,33</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-8,84; 1,26</t>
+          <t>-8,89; 1,33</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-1,68; 10,64</t>
+          <t>-1,75; 9,95</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-13,6; -0,04</t>
+          <t>-11,96; 0,22</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1060,22 +1060,22 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 35,39</t>
+          <t>0,0; 28,91</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-3,02; 19,66</t>
+          <t>-4,04; 19,26</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-13,24; 0,0</t>
+          <t>-14,02; 0,0</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-3,29; 8,52</t>
+          <t>-2,78; 9,07</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1102,7 +1102,7 @@
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>Jaen</t>
+          <t>Jaén</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1160,22 +1160,22 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-8,72; 0,0</t>
+          <t>-9,98; 0,0</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-3,14; 10,87</t>
+          <t>-3,18; 10,65</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-4,31; 12,6</t>
+          <t>-3,34; 12,47</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-13,09; 5,27</t>
+          <t>-13,86; 5,45</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1195,14 +1195,14 @@
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-70,62; 68,67</t>
+          <t>-74,9; 67,9</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Malaga</t>
+          <t>Málaga</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-5,2; 2,47</t>
+          <t>-5,76; 2,47</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-1,42; 6,49</t>
+          <t>-1,51; 6,03</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-5,15; 2,7</t>
+          <t>-5,22; 2,96</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-5,82; 8,61</t>
+          <t>-5,66; 8,6</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-86,1; 244,77</t>
+          <t>-87,45; 185,02</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-56,88; 883,58</t>
+          <t>-67,48; 670,34</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-88,64; 244,73</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-58,79; 249,93</t>
+          <t>-55,23; 250,0</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-9,41; 0,33</t>
+          <t>-8,57; 1,19</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-5,49; 1,09</t>
+          <t>-5,49; 1,17</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-0,87; 4,47</t>
+          <t>-0,76; 4,6</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-3,81; 4,22</t>
+          <t>-4,1; 3,93</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-95,11; 41,87</t>
+          <t>-91,95; 50,64</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 93,73</t>
+          <t>-100,0; 110,23</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-95,43; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-67,2; 249,03</t>
+          <t>-67,41; 241,66</t>
         </is>
       </c>
     </row>
@@ -1460,42 +1460,42 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-3,26; -0,1</t>
+          <t>-3,54; -0,31</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-2,58; 1,04</t>
+          <t>-2,61; 1,08</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-1,07; 2,18</t>
+          <t>-1,2; 1,97</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-3,21; 1,41</t>
+          <t>-3,54; 1,22</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-74,84; -0,71</t>
+          <t>-74,73; -7,79</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-56,6; 38,77</t>
+          <t>-57,32; 43,35</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-41,46; 138,67</t>
+          <t>-44,88; 137,13</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-43,62; 28,75</t>
+          <t>-45,97; 26,83</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P2A_fisi_R-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/P2A_fisi_R-Provincia-trans_bre.xlsx
@@ -660,22 +660,22 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-7,46; 2,02</t>
+          <t>-7,47; 1,53</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-16,88; 0,6</t>
+          <t>-15,01; 1,16</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-9,06; 4,68</t>
+          <t>-9,68; 4,97</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-9,3; 0,08</t>
+          <t>-9,83; 0,03</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -690,12 +690,12 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 276,31</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; —</t>
         </is>
       </c>
     </row>
@@ -760,22 +760,22 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-6,66; 3,24</t>
+          <t>-6,05; 3,47</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-9,68; 0,2</t>
+          <t>-10,6; 0,1</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-1,84; 9,36</t>
+          <t>-2,32; 8,22</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-6,23; 6,0</t>
+          <t>-6,68; 6,07</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -795,7 +795,7 @@
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-71,88; 209,75</t>
+          <t>-69,19; 202,12</t>
         </is>
       </c>
     </row>
@@ -860,12 +860,12 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-6,45; 0,0</t>
+          <t>-6,46; 0,0</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-6,02; 3,3</t>
+          <t>-4,97; 4,44</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -875,7 +875,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-13,4; 0,93</t>
+          <t>-12,48; 1,07</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -895,7 +895,7 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-91,98; 37,55</t>
+          <t>-89,71; 42,82</t>
         </is>
       </c>
     </row>
@@ -960,22 +960,22 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-3,25; 3,33</t>
+          <t>-3,19; 3,96</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-8,89; 1,33</t>
+          <t>-7,79; 2,4</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-1,75; 9,95</t>
+          <t>-1,62; 10,61</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-11,96; 0,22</t>
+          <t>-12,45; 0,16</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1060,22 +1060,22 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 28,91</t>
+          <t>0,0; 31,44</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-4,04; 19,26</t>
+          <t>-2,65; 19,71</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-14,02; 0,0</t>
+          <t>-12,96; 0,0</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-2,78; 9,07</t>
+          <t>-3,2; 8,88</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1160,22 +1160,22 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-9,98; 0,0</t>
+          <t>-8,64; 0,0</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-3,18; 10,65</t>
+          <t>-2,86; 10,99</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-3,34; 12,47</t>
+          <t>-4,48; 12,2</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-13,86; 5,45</t>
+          <t>-14,34; 6,18</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1195,7 +1195,7 @@
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-74,9; 67,9</t>
+          <t>-75,65; 78,23</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-5,76; 2,47</t>
+          <t>-5,16; 2,53</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-1,51; 6,03</t>
+          <t>-1,19; 6,45</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-5,22; 2,96</t>
+          <t>-5,01; 2,89</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-5,66; 8,6</t>
+          <t>-6,77; 8,91</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-87,45; 185,02</t>
+          <t>-86,3; 187,36</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-67,48; 670,34</t>
+          <t>-54,18; 931,94</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-89,66; 294,4</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-55,23; 250,0</t>
+          <t>-62,52; 244,64</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-8,57; 1,19</t>
+          <t>-9,29; 0,47</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-5,49; 1,17</t>
+          <t>-5,5; 1,12</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-0,76; 4,6</t>
+          <t>-0,59; 4,44</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-4,1; 3,93</t>
+          <t>-3,84; 4,06</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-91,95; 50,64</t>
+          <t>-92,47; 35,96</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 110,23</t>
+          <t>-100,0; 84,53</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-72,61; —</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-67,41; 241,66</t>
+          <t>-66,26; 242,3</t>
         </is>
       </c>
     </row>
@@ -1460,42 +1460,42 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-3,54; -0,31</t>
+          <t>-3,44; -0,13</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-2,61; 1,08</t>
+          <t>-2,45; 1,14</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-1,2; 1,97</t>
+          <t>-1,13; 1,88</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-3,54; 1,22</t>
+          <t>-3,53; 1,25</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-74,73; -7,79</t>
+          <t>-74,46; -2,59</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-57,32; 43,35</t>
+          <t>-55,34; 42,99</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-44,88; 137,13</t>
+          <t>-38,88; 127,45</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-45,97; 26,83</t>
+          <t>-46,3; 25,01</t>
         </is>
       </c>
     </row>
